--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -61,22 +64,49 @@
     <t>2026-05-13</t>
   </si>
   <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
     <t>СВ6868РО</t>
   </si>
   <si>
     <t>78970153027721256</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
-    <t>4 Л. ЛЯTHA TEЧHOCT З</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>11:54</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>12:01:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>13:03:00</t>
+  </si>
+  <si>
+    <t>3231288344 3231288344</t>
+  </si>
+  <si>
+    <t>3231821655 3231821655</t>
+  </si>
+  <si>
+    <t>3232569090 3232569090</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3</t>
@@ -500,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,16 +539,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,221 +589,277 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1198</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>27.53</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>1.87</v>
+      </c>
+      <c r="I2" s="1">
+        <v>51.48</v>
+      </c>
+      <c r="J2">
         <v>2.07</v>
       </c>
-      <c r="H2">
+      <c r="K2" s="1">
         <v>56.99</v>
       </c>
-      <c r="I2" s="1">
-        <v>2.07</v>
-      </c>
-      <c r="J2">
-        <v>56.99</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>63.93</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>1.87</v>
+      </c>
+      <c r="I3" s="1">
+        <v>119.55</v>
+      </c>
+      <c r="J3">
+        <v>2.03</v>
+      </c>
+      <c r="K3" s="1">
+        <v>129.78</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>324452</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1184</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>8.99</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8.99</v>
+      </c>
+      <c r="J4">
+        <v>8.99</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.99</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5">
+        <v>1.87</v>
+      </c>
+      <c r="I5" s="1">
+        <v>120.17</v>
+      </c>
+      <c r="J5">
+        <v>1.95</v>
+      </c>
+      <c r="K5" s="1">
+        <v>125.31</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="6">
+        <v>155.72</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E10" s="6">
+        <v>291.2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>312.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="G3" s="1">
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
         <v>8.99</v>
       </c>
-      <c r="H3">
+      <c r="E11" s="6">
         <v>8.99</v>
       </c>
-      <c r="I3" s="1">
+      <c r="F11" s="6">
         <v>8.99</v>
       </c>
-      <c r="J3">
-        <v>8.99</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>86905</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1184</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>63.93</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2.03</v>
-      </c>
-      <c r="H4">
-        <v>129.78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2.03</v>
-      </c>
-      <c r="J4">
-        <v>129.78</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>86905</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="6">
-        <v>91.45999999999999</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2.0421</v>
-      </c>
-      <c r="E9" s="6">
-        <v>186.77</v>
-      </c>
-      <c r="F9" s="6">
-        <v>186.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="7">
-        <v>8.99</v>
-      </c>
-      <c r="E10" s="6">
-        <v>8.99</v>
-      </c>
-      <c r="F10" s="6">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="9">
-        <v>92.45999999999999</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>195.76</v>
-      </c>
-      <c r="F11" s="9">
-        <v>195.76</v>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="9">
+        <v>156.72</v>
+      </c>
+      <c r="C12" s="9">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>300.19</v>
+      </c>
+      <c r="F12" s="9">
+        <v>321.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,12 +170,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,17 +219,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,28 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>1198 Struma Highway</t>
-  </si>
-  <si>
-    <t>1184 София Дружба2</t>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>София Дружба 2</t>
   </si>
   <si>
     <t>СВ6868РО</t>
@@ -80,33 +62,6 @@
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
-    <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>12:01:00</t>
-  </si>
-  <si>
-    <t>11:55:00</t>
-  </si>
-  <si>
-    <t>13:03:00</t>
-  </si>
-  <si>
-    <t>3231288344 3231288344</t>
-  </si>
-  <si>
-    <t>3231821655 3231821655</t>
-  </si>
-  <si>
-    <t>3232569090 3232569090</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3</t>
@@ -524,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,17 +488,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,283 +529,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>65.59</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="H2">
+        <v>121.34</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="J2">
+        <v>122</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
+        <v>65.59</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="E7" s="6">
+        <v>121.34</v>
+      </c>
+      <c r="F7" s="6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>27.53</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
-        <v>1.87</v>
-      </c>
-      <c r="I2" s="1">
-        <v>51.48</v>
-      </c>
-      <c r="J2">
-        <v>2.07</v>
-      </c>
-      <c r="K2" s="1">
-        <v>56.99</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>63.93</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>1.87</v>
-      </c>
-      <c r="I3" s="1">
-        <v>119.55</v>
-      </c>
-      <c r="J3">
-        <v>2.03</v>
-      </c>
-      <c r="K3" s="1">
-        <v>129.78</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
+      <c r="B8" s="9">
+        <v>65.59</v>
+      </c>
+      <c r="C8" s="9">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>8.99</v>
-      </c>
-      <c r="I4" s="1">
-        <v>8.99</v>
-      </c>
-      <c r="J4">
-        <v>8.99</v>
-      </c>
-      <c r="K4" s="1">
-        <v>8.99</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
-        <v>1.87</v>
-      </c>
-      <c r="I5" s="1">
-        <v>120.17</v>
-      </c>
-      <c r="J5">
-        <v>1.95</v>
-      </c>
-      <c r="K5" s="1">
-        <v>125.31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="6">
-        <v>155.72</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="E10" s="6">
-        <v>291.2</v>
-      </c>
-      <c r="F10" s="6">
-        <v>312.08</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7">
-        <v>8.99</v>
-      </c>
-      <c r="E11" s="6">
-        <v>8.99</v>
-      </c>
-      <c r="F11" s="6">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="9">
-        <v>156.72</v>
-      </c>
-      <c r="C12" s="9">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>300.19</v>
-      </c>
-      <c r="F12" s="9">
-        <v>321.07</v>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9">
+        <v>121.34</v>
+      </c>
+      <c r="F8" s="9">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,22 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-12</t>
   </si>
   <si>
-    <t>София Дружба 2</t>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1149 Кюстендил Николичевски път</t>
   </si>
   <si>
     <t>СВ6868РО</t>
@@ -64,7 +79,25 @@
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-06-12 08:36:43</t>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>08:36:00</t>
+  </si>
+  <si>
+    <t>10:37:00</t>
+  </si>
+  <si>
+    <t>3233242932 3233242932</t>
+  </si>
+  <si>
+    <t>3233958170 3233958170</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3</t>
@@ -482,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,14 +524,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -532,113 +568,239 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>65.59</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.8</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>118.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.86</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>122</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="3" t="s">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>60.42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
+        <v>1.7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>102.71</v>
+      </c>
+      <c r="J3">
+        <v>1.77</v>
+      </c>
+      <c r="K3" s="1">
+        <v>106.94</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>4.09</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8.18</v>
+      </c>
+      <c r="J4">
+        <v>4.09</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="B9" s="6">
+        <v>126.01</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.752</v>
+      </c>
+      <c r="E9" s="6">
+        <v>220.77</v>
+      </c>
+      <c r="F9" s="6">
+        <v>228.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B10" s="6">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="E10" s="6">
+        <v>8.18</v>
+      </c>
+      <c r="F10" s="6">
+        <v>8.18</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6">
-        <v>65.59</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="6">
-        <v>118.06</v>
-      </c>
-      <c r="F7" s="6">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="9">
-        <v>65.59</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>118.06</v>
-      </c>
-      <c r="F8" s="9">
-        <v>122</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="9">
+        <v>128.01</v>
+      </c>
+      <c r="C11" s="9">
+        <v>3</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>228.95</v>
+      </c>
+      <c r="F11" s="9">
+        <v>237.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,16 +55,25 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Свиленград</t>
-  </si>
-  <si>
-    <t>София Асен Йорданов</t>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>1177 Свиленград</t>
+  </si>
+  <si>
+    <t>1917 бул. Асен Йорданов</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
   </si>
   <si>
     <t>СВ6868РО</t>
@@ -73,16 +85,34 @@
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>XAPTИEH APOMATИЗATOP CПEЦИAЛHA CEЛEKЦИЯ</t>
-  </si>
-  <si>
-    <t>2026-07-03 09:01:03</t>
-  </si>
-  <si>
-    <t>2026-07-15 17:26:31</t>
-  </si>
-  <si>
-    <t>2026-07-15 17:26:55</t>
+    <t>PAPER AIR FRESHENER SPECIAL SELECTION</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>17:26:00</t>
+  </si>
+  <si>
+    <t>21:32:00</t>
+  </si>
+  <si>
+    <t>3234242281 3234242281</t>
+  </si>
+  <si>
+    <t>3234816677 3234816677</t>
+  </si>
+  <si>
+    <t>3234816678 3234816678</t>
+  </si>
+  <si>
+    <t>3235496519 3235496519</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3</t>
@@ -500,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,15 +539,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,104 +586,122 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>40.62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.7</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>69.05</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.77</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>71.90000000000001</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>66</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.68</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>110.88</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.83</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>120.78</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="1">
-        <v>1.32</v>
+      <c r="G4" t="s">
+        <v>25</v>
       </c>
       <c r="H4">
         <v>1.32</v>
@@ -662,104 +712,154 @@
       <c r="J4">
         <v>1.32</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="L4">
+      <c r="F5">
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>1.78</v>
+      </c>
+      <c r="I5" s="1">
+        <v>113.92</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>128</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6">
+        <v>170.62</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.7222</v>
+      </c>
+      <c r="E10" s="6">
+        <v>293.85</v>
+      </c>
+      <c r="F10" s="6">
+        <v>320.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="6">
-        <v>106.62</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.6876</v>
-      </c>
-      <c r="E9" s="6">
-        <v>179.93</v>
-      </c>
-      <c r="F9" s="6">
-        <v>192.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="7">
         <v>1.32</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E11" s="6">
         <v>1.32</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F11" s="6">
         <v>1.32</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="9">
-        <v>107.62</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>181.25</v>
-      </c>
-      <c r="F11" s="9">
-        <v>194</v>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="9">
+        <v>171.62</v>
+      </c>
+      <c r="C12" s="9">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>295.17</v>
+      </c>
+      <c r="F12" s="9">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -139,7 +139,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>1.7222</v>
+        <v>1.722248</v>
       </c>
       <c r="E10" s="6">
         <v>293.85</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -530,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -543,13 +546,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -592,116 +595,125 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>40.621</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.619</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.699</v>
+      </c>
+      <c r="J2">
+        <v>69.015079</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L2" s="1">
+        <v>71.89917</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>40.62</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>1.7</v>
-      </c>
-      <c r="I2" s="1">
-        <v>69.05</v>
-      </c>
-      <c r="J2">
-        <v>1.77</v>
-      </c>
-      <c r="K2" s="1">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>66</v>
       </c>
       <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>1.599</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.679</v>
+      </c>
+      <c r="J3">
+        <v>110.814</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="L3" s="1">
+        <v>120.78</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.68</v>
-      </c>
-      <c r="I3" s="1">
-        <v>110.88</v>
-      </c>
-      <c r="J3">
-        <v>1.83</v>
-      </c>
-      <c r="K3" s="1">
-        <v>120.78</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>1.32</v>
@@ -715,63 +727,69 @@
       <c r="K4" s="1">
         <v>1.32</v>
       </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>1.78</v>
+        <v>1.702</v>
       </c>
       <c r="I5" s="1">
-        <v>113.92</v>
+        <v>1.782</v>
       </c>
       <c r="J5">
+        <v>114.048</v>
+      </c>
+      <c r="K5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>128</v>
       </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -779,49 +797,49 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6">
-        <v>170.62</v>
+        <v>170.621</v>
       </c>
       <c r="C10" s="6">
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>1.722248</v>
+        <v>1.722397</v>
       </c>
       <c r="E10" s="6">
-        <v>293.85</v>
+        <v>293.88</v>
       </c>
       <c r="F10" s="6">
         <v>320.68</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6">
         <v>1</v>
@@ -839,19 +857,19 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9">
-        <v>171.62</v>
+        <v>171.621</v>
       </c>
       <c r="C12" s="9">
         <v>4</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>295.17</v>
+        <v>295.2</v>
       </c>
       <c r="F12" s="9">
         <v>322</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -141,8 +138,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -235,10 +232,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -546,13 +543,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -595,125 +592,116 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
       </c>
       <c r="F2">
         <v>40.621</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2">
-        <v>1.619</v>
+        <v>1.699</v>
       </c>
       <c r="I2" s="1">
-        <v>1.699</v>
+        <v>69.015</v>
       </c>
       <c r="J2">
-        <v>69.015079</v>
+        <v>1.77</v>
       </c>
       <c r="K2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L2" s="1">
-        <v>71.89917</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
+        <v>71.899</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I3" s="1">
-        <v>1.679</v>
+        <v>110.814</v>
       </c>
       <c r="J3">
-        <v>110.814</v>
+        <v>1.83</v>
       </c>
       <c r="K3" s="1">
-        <v>1.83</v>
-      </c>
-      <c r="L3" s="1">
         <v>120.78</v>
       </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>1.32</v>
@@ -727,69 +715,63 @@
       <c r="K4" s="1">
         <v>1.32</v>
       </c>
-      <c r="L4" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
       <c r="F5">
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>1.702</v>
+        <v>1.782</v>
       </c>
       <c r="I5" s="1">
-        <v>1.782</v>
+        <v>114.048</v>
       </c>
       <c r="J5">
-        <v>114.048</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>2</v>
-      </c>
-      <c r="L5" s="1">
         <v>128</v>
       </c>
-      <c r="M5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -797,69 +779,69 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="6">
         <v>170.621</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>1.722397</v>
-      </c>
-      <c r="E10" s="6">
-        <v>293.88</v>
-      </c>
-      <c r="F10" s="6">
-        <v>320.68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>1.722</v>
+      </c>
+      <c r="E10" s="7">
+        <v>293.877</v>
+      </c>
+      <c r="F10" s="7">
+        <v>320.679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="7">
         <v>1.32</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>1.32</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>1.32</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="9">
         <v>171.621</v>
@@ -869,10 +851,10 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>295.2</v>
+        <v>295.197</v>
       </c>
       <c r="F12" s="9">
-        <v>322</v>
+        <v>321.999</v>
       </c>
     </row>
   </sheetData>
